--- a/teacher_forms/004_cross_cultural_teaching_assistance_request_form--teacher_forms.xlsx
+++ b/teacher_forms/004_cross_cultural_teaching_assistance_request_form--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Teachers Name</t>
+          <t>Teacher Name2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Subject</t>
+          <t>Subject2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Course Title</t>
+          <t>Course Title2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Number of Students</t>
+          <t>Course Number2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Teaching Level</t>
+          <t>Teaching Level2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Time2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Classroom Details</t>
+          <t>Classroom Details2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Additional Information</t>
+          <t>Additional Info2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Support Type</t>
+          <t>Support Type2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'elementary',_'value':_'elementary'}</t>
+          <t>elementary</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Elementary', 'value': 'elementary'}</t>
+          <t>Elementary</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'high_school',_'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'High School', 'value': 'high_school'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'college',_'value':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'College', 'value': 'college'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'university',_'value':_'university'}</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'University', 'value': 'university'}</t>
+          <t>University</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'one-on-one_support',_'value':_'one-on-one'}</t>
+          <t>one-on-one_support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'One-on-one Support', 'value': 'one-on-one'}</t>
+          <t>One-on-one Support</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'group_support',_'value':_'group'}</t>
+          <t>group_support</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Group Support', 'value': 'group'}</t>
+          <t>Group Support</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'None', 'value': 'none'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'elementary',_'value':_'elementary'}</t>
+          <t>elementary</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Elementary', 'value': 'elementary'}</t>
+          <t>Elementary</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'high_school',_'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'High School', 'value': 'high_school'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'college',_'value':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'College', 'value': 'college'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'university',_'value':_'university'}</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'University', 'value': 'university'}</t>
+          <t>University</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'one-on-one_support',_'value':_'one-on-one'}</t>
+          <t>one-on-one_support</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'One-on-one Support', 'value': 'one-on-one'}</t>
+          <t>One-on-one Support</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'group_support',_'value':_'group'}</t>
+          <t>group_support</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Group Support', 'value': 'group'}</t>
+          <t>Group Support</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'both',_'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Both', 'value': 'both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'None', 'value': 'none'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
